--- a/interview_database.xlsx
+++ b/interview_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Baja Drive\Interview-Backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82C05FD0-8B37-4D03-A8C0-C53123276CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB0FB50-9695-48B3-AFBF-28DFF3A1840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{CF3DA4E5-7533-4167-BFC9-F110553E4FC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF3DA4E5-7533-4167-BFC9-F110553E4FC5}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>UUID</t>
   </si>
@@ -81,6 +81,24 @@
   </si>
   <si>
     <t>ali@gmail.com, jhon1@gmail.com</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Eng</t>
+  </si>
+  <si>
+    <t>Eng@gmail.com</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Business</t>
   </si>
 </sst>
 </file>
@@ -465,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7E29F2-351E-41EE-8CB6-D6CE839D80D3}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="50" bestFit="1" customWidth="1"/>
@@ -523,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -536,11 +554,82 @@
       </c>
       <c r="I2" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>12346</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.35625000000000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45689</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>12347</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.23125000000000001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45689</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" display="hamod@gmail.com, " xr:uid="{B0952193-00FF-47D8-9F07-3FFE6602B2BF}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{D0597C4F-41EC-447E-9CC8-658984547DFA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/interview_database.xlsx
+++ b/interview_database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,14 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,19 +70,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -442,8 +453,8 @@
   <cols>
     <col width="13.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="37.140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="8.5703125" customWidth="1" min="7" max="7"/>
+    <col width="31" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="73.42578125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,12 +569,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zoz, Alice Johnson, Charlie Brown</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Zoz@example.com, darkicewolf50@gmail.com, charlie.brown@example.com</t>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>ahmadmuhammadofficial@gmail.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -741,16 +752,6 @@
       </c>
       <c r="C9" s="3" t="n">
         <v>0.5625</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bob Smith</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ahmadmuhammadofficial@gmail.com</t>
-        </is>
       </c>
       <c r="I9" t="n">
         <v>1</v>

--- a/interview_database.xlsx
+++ b/interview_database.xlsx
@@ -568,12 +568,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zoz, Alice Johnson, Alice Johnson</t>
+          <t>Zoz, Alice Johnson, Alice Johnson, Alice Johnson, Alice Johnson, Alice Johnson, Alice Johnson, Alice Johnson</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zoz@example.com, ahmadmuhammadofficial@gmail.com, darkicewolf50@gmail.com</t>
+          <t>Zoz@example.com, ahmadmuhammadofficial@gmail.com, darkicewolf50@gmail.com, darkicewolf50@gmail.com, darkicewolf50@gmail.coaaaa, darkicewolf50@gma.com, darkicewolf50@gma.com, darkicewolf50@gma.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
